--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3665,6 +3665,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F95" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J95" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J95"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3699,6 +3699,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F96" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J96" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3733,6 +3733,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F97" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J97" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3767,6 +3767,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F98" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J98" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3801,6 +3801,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F99" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J99" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3835,6 +3835,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F100" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J100" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3869,6 +3869,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F101" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J101" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3903,6 +3903,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F102" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J102" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3937,6 +3937,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F103" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J103" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3971,6 +3971,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F104" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J104" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4005,6 +4005,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F105" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J105" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4039,6 +4039,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F106" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J106" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4073,6 +4073,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F107" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J107" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4107,6 +4107,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F108" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J108" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4141,6 +4141,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F109" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J109" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4175,6 +4175,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F110" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J110" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4209,6 +4209,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F111" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J111" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4243,6 +4243,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F112" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J112" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4277,6 +4277,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F113" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J113" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4311,6 +4311,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F114" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J114" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4345,6 +4345,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F115" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J115" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4379,6 +4379,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F116" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J116" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4413,6 +4413,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F117" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J117" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4447,6 +4447,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F118" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J118" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4481,6 +4481,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F119" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J119" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4515,6 +4515,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F120" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J120" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4549,6 +4549,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F121" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J121" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4583,6 +4583,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F122" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J122" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4617,6 +4617,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F123" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J123" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4651,6 +4651,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F124" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J124" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4685,6 +4685,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F125" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J125" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4719,6 +4719,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F126" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J126" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4753,6 +4753,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>32.63</v>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F127" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>29.37</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J127" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4787,6 +4787,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F128" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J128" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4821,6 +4821,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F129" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J129" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4855,6 +4855,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F130" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J130" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4889,6 +4889,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F131" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J131" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4923,6 +4923,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F132" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J132" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4957,6 +4957,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>31.55</v>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F133" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J133" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4991,6 +4991,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F134" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J134" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5025,6 +5025,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F135" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J135" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5059,6 +5059,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C136" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F136" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J136" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5093,6 +5093,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F137" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J137" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5127,6 +5127,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F138" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J138" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5161,6 +5161,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F139" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J139" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5195,6 +5195,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F140" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J140" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5229,6 +5229,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F141" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J141" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5263,6 +5263,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/咖啡豆每日价格.xlsx
+++ b/咖啡豆每日价格.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:J143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5297,6 +5297,40 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="F143" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="J143" s="2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
